--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/NEBRASKA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/NEBRASKA_2013.xlsx
@@ -1698,7 +1698,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C75">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C116">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C140">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C474">
@@ -11533,7 +11533,7 @@
         <v>41</v>
       </c>
       <c r="D621">
-        <v>0.00955710955711</v>
+        <v>0.009557109557110002</v>
       </c>
     </row>
     <row r="622">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C668">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C729">
